--- a/next_podiums.xlsx
+++ b/next_podiums.xlsx
@@ -133,14 +133,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -927,7 +927,7 @@
           <t>6630</t>
         </is>
       </c>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t>9855</t>
         </is>
@@ -1732,7 +1732,7 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="L43" s="15" t="inlineStr">
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>9920</t>
         </is>
@@ -3129,7 +3129,7 @@
           <t>7531</t>
         </is>
       </c>
-      <c r="J80" s="7" t="inlineStr">
+      <c r="J80" s="16" t="inlineStr">
         <is>
           <t>8633</t>
         </is>
@@ -5565,7 +5565,7 @@
           <t>9864</t>
         </is>
       </c>
-      <c r="J148" s="7" t="inlineStr">
+      <c r="J148" s="16" t="inlineStr">
         <is>
           <t>8644</t>
         </is>
@@ -7044,7 +7044,7 @@
           <t>9872</t>
         </is>
       </c>
-      <c r="M191" s="15" t="inlineStr">
+      <c r="M191" s="7" t="inlineStr">
         <is>
           <t>7522</t>
         </is>
@@ -7606,7 +7606,7 @@
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1" s="6">
-      <c r="D208" s="7" t="inlineStr">
+      <c r="D208" s="16" t="inlineStr">
         <is>
           <t>9940</t>
         </is>
@@ -7822,7 +7822,7 @@
           <t>9410</t>
         </is>
       </c>
-      <c r="P211" s="15" t="inlineStr">
+      <c r="P211" s="7" t="inlineStr">
         <is>
           <t>8862</t>
         </is>
@@ -8013,7 +8013,7 @@
           <t>5100</t>
         </is>
       </c>
-      <c r="J218" s="7" t="inlineStr">
+      <c r="J218" s="16" t="inlineStr">
         <is>
           <t>8833</t>
         </is>
@@ -8149,12 +8149,12 @@
           <t>9411</t>
         </is>
       </c>
-      <c r="I221" s="15" t="inlineStr">
+      <c r="I221" s="7" t="inlineStr">
         <is>
           <t>7731</t>
         </is>
       </c>
-      <c r="J221" s="15" t="inlineStr">
+      <c r="J221" s="7" t="inlineStr">
         <is>
           <t>8851</t>
         </is>
@@ -8169,7 +8169,7 @@
           <t>9862</t>
         </is>
       </c>
-      <c r="N221" s="15" t="inlineStr">
+      <c r="N221" s="7" t="inlineStr">
         <is>
           <t>6653</t>
         </is>
@@ -8481,7 +8481,7 @@
           <t>8520</t>
         </is>
       </c>
-      <c r="I231" s="15" t="inlineStr">
+      <c r="I231" s="7" t="inlineStr">
         <is>
           <t>8853</t>
         </is>
@@ -9044,7 +9044,7 @@
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1" s="6">
-      <c r="D248" s="7" t="inlineStr">
+      <c r="D248" s="16" t="inlineStr">
         <is>
           <t>9722</t>
         </is>
@@ -9592,7 +9592,7 @@
           <t>5522</t>
         </is>
       </c>
-      <c r="P261" s="15" t="inlineStr">
+      <c r="P261" s="7" t="inlineStr">
         <is>
           <t>6664</t>
         </is>
@@ -9924,7 +9924,7 @@
           <t>9872</t>
         </is>
       </c>
-      <c r="P271" s="15" t="inlineStr">
+      <c r="P271" s="7" t="inlineStr">
         <is>
           <t>8110</t>
         </is>
@@ -10929,7 +10929,7 @@
           <t>9876</t>
         </is>
       </c>
-      <c r="R300" s="8" t="inlineStr">
+      <c r="R300" s="7" t="inlineStr">
         <is>
           <t>9644</t>
         </is>
@@ -11482,7 +11482,7 @@
           <t>6400</t>
         </is>
       </c>
-      <c r="J317" s="7" t="inlineStr">
+      <c r="J317" s="16" t="inlineStr">
         <is>
           <t>9722</t>
         </is>
@@ -11849,7 +11849,7 @@
           <t>9760</t>
         </is>
       </c>
-      <c r="L327" s="7" t="inlineStr">
+      <c r="L327" s="16" t="inlineStr">
         <is>
           <t>8842</t>
         </is>
@@ -11975,7 +11975,7 @@
       </c>
     </row>
     <row r="330" ht="14.25" customHeight="1" s="6">
-      <c r="H330" s="15" t="inlineStr">
+      <c r="H330" s="7" t="inlineStr">
         <is>
           <t>6653</t>
         </is>
@@ -12317,7 +12317,7 @@
           <t>9332</t>
         </is>
       </c>
-      <c r="J340" s="15" t="inlineStr">
+      <c r="J340" s="7" t="inlineStr">
         <is>
           <t>8622</t>
         </is>
@@ -12870,7 +12870,7 @@
           <t>8776</t>
         </is>
       </c>
-      <c r="R357" s="7" t="inlineStr">
+      <c r="R357" s="16" t="inlineStr">
         <is>
           <t>6640</t>
         </is>
@@ -14168,7 +14168,7 @@
           <t>7531</t>
         </is>
       </c>
-      <c r="J397" s="7" t="inlineStr">
+      <c r="J397" s="16" t="inlineStr">
         <is>
           <t>9544</t>
         </is>
@@ -14505,7 +14505,7 @@
           <t>6432</t>
         </is>
       </c>
-      <c r="L407" s="7" t="inlineStr">
+      <c r="L407" s="16" t="inlineStr">
         <is>
           <t>9544</t>
         </is>
@@ -16600,7 +16600,7 @@
           <t>9541</t>
         </is>
       </c>
-      <c r="P466" s="7" t="inlineStr">
+      <c r="P466" s="16" t="inlineStr">
         <is>
           <t>9744</t>
         </is>
@@ -17064,7 +17064,7 @@
           <t>8620</t>
         </is>
       </c>
-      <c r="M480" s="15" t="inlineStr">
+      <c r="M480" s="7" t="inlineStr">
         <is>
           <t>8851</t>
         </is>
@@ -17606,7 +17606,7 @@
           <t>9321</t>
         </is>
       </c>
-      <c r="R496" s="7" t="inlineStr">
+      <c r="R496" s="16" t="inlineStr">
         <is>
           <t>7742</t>
         </is>
@@ -17707,7 +17707,7 @@
       </c>
     </row>
     <row r="499" ht="14.25" customHeight="1" s="6">
-      <c r="H499" s="15" t="inlineStr">
+      <c r="H499" s="7" t="inlineStr">
         <is>
           <t>6330</t>
         </is>
@@ -18314,7 +18314,7 @@
           <t>7632</t>
         </is>
       </c>
-      <c r="N515" s="7" t="inlineStr">
+      <c r="N515" s="16" t="inlineStr">
         <is>
           <t>7731</t>
         </is>
@@ -18465,7 +18465,7 @@
           <t>7500</t>
         </is>
       </c>
-      <c r="I518" s="15" t="inlineStr">
+      <c r="I518" s="7" t="inlineStr">
         <is>
           <t>9522</t>
         </is>
@@ -21404,7 +21404,7 @@
           <t>9740</t>
         </is>
       </c>
-      <c r="N591" s="15" t="inlineStr">
+      <c r="N591" s="7" t="inlineStr">
         <is>
           <t>7331</t>
         </is>
@@ -21725,7 +21725,7 @@
           <t>8520</t>
         </is>
       </c>
-      <c r="L600" s="15" t="inlineStr">
+      <c r="L600" s="7" t="inlineStr">
         <is>
           <t>9991</t>
         </is>
@@ -21930,7 +21930,7 @@
           <t>5440</t>
         </is>
       </c>
-      <c r="P606" s="7" t="inlineStr">
+      <c r="P606" s="16" t="inlineStr">
         <is>
           <t>9544</t>
         </is>
@@ -22041,7 +22041,7 @@
       </c>
     </row>
     <row r="609" ht="14.25" customHeight="1" s="6">
-      <c r="H609" s="15" t="inlineStr">
+      <c r="H609" s="7" t="inlineStr">
         <is>
           <t>8422</t>
         </is>
@@ -22076,7 +22076,7 @@
           <t>5541</t>
         </is>
       </c>
-      <c r="Q609" s="8" t="inlineStr">
+      <c r="Q609" s="7" t="inlineStr">
         <is>
           <t>8744</t>
         </is>
@@ -23069,7 +23069,7 @@
           <t>6210</t>
         </is>
       </c>
-      <c r="Q636" s="15" t="inlineStr">
+      <c r="Q636" s="7" t="inlineStr">
         <is>
           <t>7522</t>
         </is>
@@ -25325,7 +25325,7 @@
           <t>7751</t>
         </is>
       </c>
-      <c r="N696" s="7" t="inlineStr">
+      <c r="N696" s="16" t="inlineStr">
         <is>
           <t>9940</t>
         </is>
@@ -25676,7 +25676,7 @@
       </c>
     </row>
     <row r="705" ht="14.25" customHeight="1" s="6">
-      <c r="D705" s="7" t="inlineStr">
+      <c r="D705" s="16" t="inlineStr">
         <is>
           <t>9733</t>
         </is>
@@ -25731,7 +25731,7 @@
           <t>5300</t>
         </is>
       </c>
-      <c r="R705" s="7" t="inlineStr">
+      <c r="R705" s="16" t="inlineStr">
         <is>
           <t>6640</t>
         </is>
@@ -25857,7 +25857,7 @@
           <t>8876</t>
         </is>
       </c>
-      <c r="F708" s="15" t="inlineStr">
+      <c r="F708" s="7" t="inlineStr">
         <is>
           <t>6653</t>
         </is>
@@ -26077,7 +26077,7 @@
           <t>9833</t>
         </is>
       </c>
-      <c r="N714" s="7" t="inlineStr">
+      <c r="N714" s="16" t="inlineStr">
         <is>
           <t>8831</t>
         </is>
@@ -26208,7 +26208,7 @@
           <t>7662</t>
         </is>
       </c>
-      <c r="L717" s="15" t="inlineStr">
+      <c r="L717" s="7" t="inlineStr">
         <is>
           <t>6655</t>
         </is>
@@ -26388,7 +26388,7 @@
           <t>9743</t>
         </is>
       </c>
-      <c r="I723" s="7" t="inlineStr">
+      <c r="I723" s="8" t="inlineStr">
         <is>
           <t>9855</t>
         </is>
@@ -27070,7 +27070,7 @@
           <t>6510</t>
         </is>
       </c>
-      <c r="N741" s="7" t="inlineStr">
+      <c r="N741" s="16" t="inlineStr">
         <is>
           <t>8644</t>
         </is>
@@ -27401,7 +27401,7 @@
           <t>6643</t>
         </is>
       </c>
-      <c r="N750" s="7" t="inlineStr">
+      <c r="N750" s="16" t="inlineStr">
         <is>
           <t>9942</t>
         </is>
@@ -27732,7 +27732,7 @@
           <t>6542</t>
         </is>
       </c>
-      <c r="N759" s="7" t="inlineStr">
+      <c r="N759" s="8" t="inlineStr">
         <is>
           <t>9550</t>
         </is>
@@ -27747,7 +27747,7 @@
           <t>7610</t>
         </is>
       </c>
-      <c r="R759" s="7" t="inlineStr">
+      <c r="R759" s="8" t="inlineStr">
         <is>
           <t>7550</t>
         </is>
@@ -29287,7 +29287,7 @@
           <t>9871</t>
         </is>
       </c>
-      <c r="N798" s="15" t="inlineStr">
+      <c r="N798" s="7" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
@@ -29803,7 +29803,7 @@
           <t>9653</t>
         </is>
       </c>
-      <c r="M813" s="7" t="inlineStr">
+      <c r="M813" s="16" t="inlineStr">
         <is>
           <t>9744</t>
         </is>
@@ -29964,7 +29964,7 @@
           <t>6661</t>
         </is>
       </c>
-      <c r="R816" s="8" t="inlineStr">
+      <c r="R816" s="7" t="inlineStr">
         <is>
           <t>7440</t>
         </is>
@@ -30811,7 +30811,7 @@
           <t>8300</t>
         </is>
       </c>
-      <c r="Q840" s="7" t="inlineStr">
+      <c r="Q840" s="16" t="inlineStr">
         <is>
           <t>8833</t>
         </is>
@@ -31769,7 +31769,7 @@
       </c>
     </row>
     <row r="867" ht="14.25" customHeight="1" s="6">
-      <c r="H867" s="7" t="inlineStr">
+      <c r="H867" s="16" t="inlineStr">
         <is>
           <t>8842</t>
         </is>
@@ -31809,7 +31809,7 @@
           <t>8730</t>
         </is>
       </c>
-      <c r="R867" s="7" t="inlineStr">
+      <c r="R867" s="16" t="inlineStr">
         <is>
           <t>7742</t>
         </is>
@@ -31920,7 +31920,7 @@
           <t>8765</t>
         </is>
       </c>
-      <c r="J870" s="15" t="inlineStr">
+      <c r="J870" s="7" t="inlineStr">
         <is>
           <t>8851</t>
         </is>
@@ -32466,7 +32466,7 @@
           <t>7653</t>
         </is>
       </c>
-      <c r="Q885" s="7" t="inlineStr">
+      <c r="Q885" s="16" t="inlineStr">
         <is>
           <t>8644</t>
         </is>
@@ -32607,7 +32607,7 @@
           <t>8540</t>
         </is>
       </c>
-      <c r="Q888" s="15" t="inlineStr">
+      <c r="Q888" s="7" t="inlineStr">
         <is>
           <t>8622</t>
         </is>
@@ -34201,7 +34201,7 @@
           <t>7432</t>
         </is>
       </c>
-      <c r="N930" s="7" t="inlineStr">
+      <c r="N930" s="16" t="inlineStr">
         <is>
           <t>9544</t>
         </is>
@@ -34317,7 +34317,7 @@
       </c>
     </row>
     <row r="933" ht="14.25" customHeight="1" s="6">
-      <c r="H933" s="15" t="inlineStr">
+      <c r="H933" s="7" t="inlineStr">
         <is>
           <t>6655</t>
         </is>
@@ -35340,7 +35340,7 @@
           <t>9530</t>
         </is>
       </c>
-      <c r="P960" s="15" t="inlineStr">
+      <c r="P960" s="7" t="inlineStr">
         <is>
           <t>6655</t>
         </is>
@@ -35681,7 +35681,7 @@
           <t>8321</t>
         </is>
       </c>
-      <c r="R969" s="15" t="inlineStr">
+      <c r="R969" s="7" t="inlineStr">
         <is>
           <t>7740</t>
         </is>
@@ -36218,7 +36218,7 @@
           <t>7762</t>
         </is>
       </c>
-      <c r="F985" s="7" t="inlineStr">
+      <c r="F985" s="16" t="inlineStr">
         <is>
           <t>9942</t>
         </is>
@@ -36950,7 +36950,7 @@
           <t>7542</t>
         </is>
       </c>
-      <c r="Q1003" s="7" t="inlineStr">
+      <c r="Q1003" s="16" t="inlineStr">
         <is>
           <t>8644</t>
         </is>
@@ -37061,12 +37061,12 @@
           <t>3320</t>
         </is>
       </c>
-      <c r="I1006" s="15" t="inlineStr">
+      <c r="I1006" s="7" t="inlineStr">
         <is>
           <t>9522</t>
         </is>
       </c>
-      <c r="J1006" s="15" t="inlineStr">
+      <c r="J1006" s="7" t="inlineStr">
         <is>
           <t>7544</t>
         </is>
@@ -37392,7 +37392,7 @@
           <t>4110</t>
         </is>
       </c>
-      <c r="I1015" s="15" t="inlineStr">
+      <c r="I1015" s="7" t="inlineStr">
         <is>
           <t>7731</t>
         </is>
@@ -37658,7 +37658,7 @@
           <t>6553</t>
         </is>
       </c>
-      <c r="M1022" s="7" t="inlineStr">
+      <c r="M1022" s="16" t="inlineStr">
         <is>
           <t>8644</t>
         </is>
@@ -38411,7 +38411,7 @@
           <t>6541</t>
         </is>
       </c>
-      <c r="M1041" s="7" t="inlineStr">
+      <c r="M1041" s="16" t="inlineStr">
         <is>
           <t>9940</t>
         </is>
@@ -38812,7 +38812,7 @@
           <t>8865</t>
         </is>
       </c>
-      <c r="H1050" s="7" t="inlineStr">
+      <c r="H1050" s="16" t="inlineStr">
         <is>
           <t>9940</t>
         </is>
@@ -40192,7 +40192,7 @@
           <t>7650</t>
         </is>
       </c>
-      <c r="I1087" s="7" t="inlineStr">
+      <c r="I1087" s="16" t="inlineStr">
         <is>
           <t>9942</t>
         </is>
@@ -40659,7 +40659,7 @@
         <v>7641</v>
       </c>
       <c r="K1099" s="10" t="n"/>
-      <c r="L1099" s="16" t="n">
+      <c r="L1099" s="10" t="n">
         <v>8330</v>
       </c>
       <c r="M1099" s="10" t="n">
@@ -41595,7 +41595,7 @@
       <c r="E1123" s="10" t="n"/>
       <c r="F1123" s="10" t="n"/>
       <c r="G1123" s="10" t="n"/>
-      <c r="H1123" s="10" t="n">
+      <c r="H1123" s="13" t="n">
         <v>8550</v>
       </c>
       <c r="I1123" s="10" t="n">
@@ -41605,7 +41605,7 @@
         <v>5443</v>
       </c>
       <c r="K1123" s="10" t="n"/>
-      <c r="L1123" s="10" t="n">
+      <c r="L1123" s="14" t="n">
         <v>9550</v>
       </c>
       <c r="M1123" s="10" t="n">
@@ -41737,7 +41737,7 @@
       <c r="L1126" s="10" t="n">
         <v>9753</v>
       </c>
-      <c r="M1126" s="13" t="n">
+      <c r="M1126" s="10" t="n">
         <v>9744</v>
       </c>
       <c r="N1126" s="10" t="n">
